--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_6_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_6_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>9</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1923,10 +1923,10 @@
         <v>20</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>15</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3491,16 +3491,16 @@
         <v>21</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X28" t="n">
         <v>9</v>
@@ -3827,16 +3827,16 @@
         <v>120</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>35</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X36" t="n">
         <v>9</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -5860,10 +5860,10 @@
         <v>15</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6454,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>89</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>29</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_6_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_6_EL.xlsx
@@ -674,10 +674,10 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
         <v>9</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3503,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="X28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,14 +4500,14 @@
         <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="AA48" t="n">
